--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Centri estivi e centri gioco (1).xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Centri estivi e centri gioco (1).xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="146">
   <si>
     <r>
       <t xml:space="preserve">
@@ -1005,8 +1005,8 @@
         <rFont val="Titillium Web"/>
       </rPr>
       <t xml:space="preserve">
-Puoi pagare direttamente in app premendo “Vedi Avviso”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
-Se hai già provveduto a pagare l'avviso ignora questo messaggio.
+Puoi pagare direttamente in app premendo “Paga”, oppure tramite tutti i canali di pagamento della piattaforma pagoPA e le altre modalità di pagamento offerte dell'ente creditore.
+Se hai già provveduto a pagare l'avviso, ignora questo messaggio.
 Per maggiori informazioni o per richiedere assistenza, contattaci tramite i canali che trovi nella scheda servizio.
 In fase di pagamento, se previsto dall'ente, l'importo riportato nel messaggio potrebbe subire variazioni.</t>
     </r>
@@ -1934,6 +1934,9 @@
     <t>Vai alla graduatoria</t>
   </si>
   <si>
+    <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
+  </si>
+  <si>
     <t>Vedi Avviso</t>
   </si>
   <si>
@@ -2914,7 +2917,7 @@
         <v>108</v>
       </c>
       <c r="K6" s="34" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L6" s="34" t="s">
         <v>108</v>
@@ -2926,12 +2929,12 @@
         <v>108</v>
       </c>
       <c r="O6" s="34" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>64</v>
@@ -2978,7 +2981,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B8" s="34" t="s">
         <v>108</v>
@@ -3025,101 +3028,101 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H9" s="34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I9" s="34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J9" s="34" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K9" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="L9" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="L9" s="34" t="s">
-        <v>123</v>
-      </c>
       <c r="M9" s="34" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N9" s="34" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O9" s="34" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H10" s="34" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I10" s="34" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J10" s="34" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K10" s="34" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L10" s="34" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M10" s="34" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N10" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="O10" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="O10" s="34" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>64</v>
@@ -3134,13 +3137,13 @@
         <v>64</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H11" s="34" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I11" s="34" t="s">
         <v>64</v>
